--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Afiliación ISAPRE</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:54</t>
+    <t xml:space="preserve">2026-08-28 15:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 15:11</t>
+    <t xml:space="preserve">2026-08-29 05:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-29 05:48</t>
+    <t xml:space="preserve">2026-09-07 13:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_s_isapre_a_2021.xlsx
@@ -2074,7 +2074,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 13:10</t>
+    <t xml:space="preserve">2026-09-08 10:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
